--- a/docs/history/intent_metrics.xlsx
+++ b/docs/history/intent_metrics.xlsx
@@ -434,7 +434,7 @@
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f>= INTENT METRICS (regenerated by tools/intent_report.py; the log is docs/history/intent_log.txt, corrections in corrections.txt)</f>
+        <f>= INTENT METRICS (regenerated by Tools/intent_report.py; the log is docs/history/intent_log.txt, corrections in corrections.txt)</f>
         <v/>
       </c>
     </row>
